--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_yearly.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -982,38 +982,42 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39364</v>
+        <v>43880</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>43913</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40582</v>
+        <v>44018</v>
       </c>
       <c r="M4" t="n">
-        <v>840</v>
+        <v>95</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="P4" t="n">
-        <v>839</v>
+        <v>94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1774193046859526</v>
+        <v>0.1312987302681531</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -1023,25 +1027,25 @@
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>485</v>
+        <v>72</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>0.6721336358454439</v>
+        <v>0.4389258158309386</v>
       </c>
       <c r="AD4" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1052,11 +1056,11 @@
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
@@ -1076,19 +1080,19 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,32 +1141,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43880</v>
+        <v>36497</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43913</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>44018</v>
+        <v>39275</v>
       </c>
       <c r="M5" t="n">
-        <v>95</v>
+        <v>1910</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.4524433971482912</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.4524433971482912</v>
       </c>
       <c r="P5" t="n">
-        <v>94</v>
+        <v>1909</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1312987302681531</v>
+        <v>0.2346677038916514</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -1172,25 +1176,25 @@
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>659</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.4524433971482912</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.4524433971482912</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>72</v>
+        <v>1251</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>0.4389258158309386</v>
+        <v>0.8262952081884098</v>
       </c>
       <c r="AD5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1209,19 +1213,19 @@
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1233,11 +1237,11 @@
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1273,49 +1277,45 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36497</v>
+        <v>36521</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>39275</v>
+        <v>40282</v>
       </c>
       <c r="M6" t="n">
-        <v>1910</v>
+        <v>2589</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4524433971482912</v>
+        <v>-0.5319062364980358</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4524433971482912</v>
+        <v>-0.5319062364980358</v>
       </c>
       <c r="P6" t="n">
-        <v>1909</v>
+        <v>2588</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2346677038916514</v>
+        <v>0.2872480347728137</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -1325,56 +1325,56 @@
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>-0.4524433971482912</v>
+        <v>-0.5319062364980358</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.4524433971482912</v>
+        <v>-0.5319062364980358</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1251</v>
+        <v>1945</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>0.8262952081884098</v>
+        <v>1.136324125574051</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1386,37 +1386,19 @@
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1426,7 +1408,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1457,7 +1439,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -1467,10 +1449,10 @@
         <v>37460</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40282</v>
+        <v>40980</v>
       </c>
       <c r="M7" t="n">
-        <v>2589</v>
+        <v>3071</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>-0.5319062364980358</v>
@@ -1479,10 +1461,10 @@
         <v>-0.5319062364980358</v>
       </c>
       <c r="P7" t="n">
-        <v>2588</v>
+        <v>3070</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2872480347728137</v>
+        <v>0.2921644649952711</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1505,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1945</v>
+        <v>2427</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
@@ -1529,35 +1511,35 @@
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1575,7 +1557,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1593,49 +1575,45 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36521</v>
+        <v>36614</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>37460</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40980</v>
+        <v>40581</v>
       </c>
       <c r="M8" t="n">
-        <v>3071</v>
+        <v>2731</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5319062364980358</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5319062364980358</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="P8" t="n">
-        <v>3070</v>
+        <v>2730</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2921644649952711</v>
+        <v>0.2449625162832292</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1645,98 +1623,80 @@
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>644</v>
+        <v>579</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>-0.5319062364980358</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.5319062364980358</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2427</v>
+        <v>2152</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>1.136324125574051</v>
+        <v>0.8705620217548211</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/5</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,7 +1706,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1777,32 +1737,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36614</v>
+        <v>36497</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>37460</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40581</v>
+        <v>40654</v>
       </c>
       <c r="M9" t="n">
-        <v>2731</v>
+        <v>2863</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4944489880306537</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4944489880306537</v>
       </c>
       <c r="P9" t="n">
-        <v>2730</v>
+        <v>2862</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2449625162832292</v>
+        <v>0.2563475356224489</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1812,32 +1772,32 @@
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>579</v>
+        <v>659</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="3" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4944489880306537</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4944489880306537</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2152</v>
+        <v>2204</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>0.8705620217548211</v>
+        <v>0.978039755285139</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
@@ -1849,35 +1809,35 @@
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1886,177 +1846,6 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36497</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40654</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2863</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4944489880306537</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4944489880306537</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2862</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2563475356224489</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>659</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" s="3" t="n">
-        <v>-0.4944489880306537</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-0.4944489880306537</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2204</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" s="3" t="n">
-        <v>0.978039755285139</v>
-      </c>
-      <c r="AD10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2069,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2546,7 +2335,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2556,7 +2345,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2567,41 +2356,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36880</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>37784</v>
+        <v>39065</v>
       </c>
       <c r="M4" t="n">
-        <v>807</v>
+        <v>1692</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2092382282226474</v>
+        <v>-0.2167155682491533</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.2320386692235181</v>
       </c>
       <c r="P4" t="n">
-        <v>281</v>
+        <v>1684</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1174267585984309</v>
+        <v>0.1744939914476272</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.07663710450244801</v>
+        <v>0.1648448146697581</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>39364</v>
@@ -2614,35 +2407,35 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>189</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>-449</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2092382282226474</v>
+        <v>-0.2167155682491533</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.2320386692235181</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>224</v>
+        <v>1503</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2646033681577118</v>
+        <v>0.276675444403685</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.2417513065725277</v>
+        <v>-0.1535435964052177</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3125104140031417</v>
+        <v>0.3050330739766358</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
@@ -2663,7 +2456,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2694,35 +2487,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36880</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>39065</v>
+        <v>39192</v>
       </c>
       <c r="M5" t="n">
-        <v>1692</v>
+        <v>1777</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2167155682491533</v>
+        <v>-0.431970132651427</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.4430822889269981</v>
       </c>
       <c r="P5" t="n">
-        <v>1684</v>
+        <v>1769</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1744939914476272</v>
+        <v>0.2308297845907774</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1648448146697581</v>
+        <v>0.2234724854190869</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>39364</v>
@@ -2735,35 +2528,35 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>189</v>
+        <v>583</v>
       </c>
       <c r="X5" t="n">
-        <v>-449</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2167155682491533</v>
+        <v>-0.431970132651427</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.4430822889269981</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1503</v>
+        <v>1194</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
         <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.276675444403685</v>
+        <v>0.7604708088110927</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1535435964052177</v>
+        <v>-0.0949159256558888</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3050330739766358</v>
+        <v>0.08977850957436206</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
@@ -2784,7 +2577,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2802,24 +2595,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -2828,26 +2617,24 @@
       <c r="K6" s="2" t="n">
         <v>37460</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>39192</v>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1777</v>
+        <v>1896</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.431970132651427</v>
+        <v>-0.5217486422257891</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.5311044950287367</v>
       </c>
       <c r="P6" t="n">
-        <v>1769</v>
+        <v>1889</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2308297845907774</v>
+        <v>0.3183884110749757</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2234724854190869</v>
+        <v>0.3183884110749757</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>39364</v>
@@ -2856,9 +2643,11 @@
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.08522544924691133</v>
+      </c>
       <c r="W6" t="n">
         <v>583</v>
       </c>
@@ -2866,46 +2655,38 @@
         <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.431970132651427</v>
+        <v>-0.5217486422257891</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.5311044950287367</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1194</v>
+        <v>1313</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
         <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.7604708088110927</v>
+        <v>1.090950676343116</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0949159256558888</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08977850957436206</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.1468353809166389</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.2227319044287797</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -2917,7 +2698,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2948,7 +2729,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -3038,7 +2819,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3056,24 +2837,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -3087,19 +2864,19 @@
         <v>1896</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.4547344877239885</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="P8" t="n">
         <v>1889</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.2744558031825254</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.2744558031825254</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>39364</v>
@@ -3111,7 +2888,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>-0.08522544924691133</v>
+        <v>-0.06129877473879142</v>
       </c>
       <c r="W8" t="n">
         <v>583</v>
@@ -3120,10 +2897,10 @@
         <v>-55</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.4547344877239885</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -3136,28 +2913,22 @@
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.090950676343116</v>
+        <v>0.8339689151178216</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>-0.04393260789245035</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.06701415450180059</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
         <v>1</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.2417513065725277</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.3125104140031417</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="b">
-        <v>1</v>
-      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -3169,7 +2940,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3200,7 +2971,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -3209,24 +2980,26 @@
       <c r="K9" s="2" t="n">
         <v>37460</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>39356</v>
+      </c>
       <c r="M9" t="n">
-        <v>1896</v>
+        <v>1890</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4547344877239885</v>
+        <v>-0.4755463220216952</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4858060135695987</v>
       </c>
       <c r="P9" t="n">
-        <v>1889</v>
+        <v>1882</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2744558031825254</v>
+        <v>0.2633859495049935</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2744558031825254</v>
+        <v>0.2629690893922373</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>39364</v>
@@ -3235,11 +3008,9 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.06129877473879142</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
         <v>583</v>
       </c>
@@ -3247,29 +3018,29 @@
         <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4547344877239885</v>
+        <v>-0.4755463220216952</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4858060135695987</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
         <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.8339689151178216</v>
+        <v>0.9067460902454902</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.04393260789245035</v>
+        <v>-0.05541932168273839</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06701415450180059</v>
+        <v>0.04620232020409387</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
@@ -3281,139 +3052,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>39356</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1890</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4755463220216952</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4858060135695987</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1882</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2633859495049935</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.2629690893922373</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>583</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-55</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.4755463220216952</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.4858060135695987</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1307</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.9067460902454902</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.05541932168273839</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.04620232020409387</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.1863319848897893</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.2663080937990479</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1083</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3426,7 +3064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3909,7 +3547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3919,7 +3557,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3930,41 +3568,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>39412</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40582</v>
+        <v>41402</v>
       </c>
       <c r="M4" t="n">
-        <v>840</v>
+        <v>1404</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="P4" t="n">
-        <v>839</v>
+        <v>1403</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.177419304685953</v>
+        <v>0.08442792929102155</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.09795419063977666</v>
+        <v>0.06024880670250294</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43364</v>
@@ -3977,40 +3619,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>485</v>
+        <v>1371</v>
       </c>
       <c r="AC4" t="n">
-        <v>-375</v>
+        <v>511</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.6721336358454448</v>
+        <v>0.1355307427048227</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.04676943834438775</v>
+        <v>-0.08447482228166148</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08648180711240072</v>
+        <v>0.3690889473104767</v>
       </c>
       <c r="AH4" t="n">
-        <v>-182</v>
+        <v>704</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4030,7 +3672,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4061,35 +3703,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>39412</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>41402</v>
+        <v>40900</v>
       </c>
       <c r="M5" t="n">
-        <v>1404</v>
+        <v>1062</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="P5" t="n">
-        <v>1403</v>
+        <v>1061</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.08442792929102155</v>
+        <v>0.1949570049202901</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.06024880670250294</v>
+        <v>0.1210123309070127</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43364</v>
@@ -4102,40 +3744,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
-        <v>-322</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1371</v>
+        <v>707</v>
       </c>
       <c r="AC5" t="n">
-        <v>511</v>
+        <v>-153</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1355307427048227</v>
+        <v>0.7718745829433944</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.08447482228166148</v>
+        <v>-0.02371129807715167</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3690889473104767</v>
+        <v>0.05281751191639561</v>
       </c>
       <c r="AH5" t="n">
-        <v>704</v>
+        <v>40</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4155,7 +3797,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4173,24 +3815,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -4200,25 +3838,25 @@
         <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40900</v>
+        <v>40094</v>
       </c>
       <c r="M6" t="n">
-        <v>1062</v>
+        <v>504</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="P6" t="n">
-        <v>1061</v>
+        <v>503</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1949570049202901</v>
+        <v>0.1066435614404946</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1210123309070127</v>
+        <v>0.0456251682558669</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43364</v>
@@ -4237,50 +3875,42 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>707</v>
+        <v>149</v>
       </c>
       <c r="AC6" t="n">
-        <v>-153</v>
+        <v>-711</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.7718745829433944</v>
+        <v>0.4023330936793994</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.02371129807715167</v>
+        <v>-0.0990984607282975</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.05281751191639561</v>
+        <v>0.2015408221558649</v>
       </c>
       <c r="AH6" t="n">
-        <v>40</v>
+        <v>-518</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.02305814026723609</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.03366429519600511</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>222</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -4292,7 +3922,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4323,7 +3953,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -4333,25 +3963,25 @@
         <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40094</v>
+        <v>40563</v>
       </c>
       <c r="M7" t="n">
-        <v>504</v>
+        <v>827</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="P7" t="n">
-        <v>503</v>
+        <v>826</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1066435614404946</v>
+        <v>0.2084343838894806</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.0456251682558669</v>
+        <v>0.1141849013605378</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43364</v>
@@ -4370,34 +4000,34 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>149</v>
+        <v>472</v>
       </c>
       <c r="AC7" t="n">
-        <v>-711</v>
+        <v>-388</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4023330936793994</v>
+        <v>0.7938399361148245</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0990984607282975</v>
+        <v>-0.0305387276236266</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2015408221558649</v>
+        <v>0.04590682013605585</v>
       </c>
       <c r="AH7" t="n">
-        <v>-518</v>
+        <v>-195</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4417,7 +4047,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4435,52 +4065,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>40361</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40563</v>
+        <v>40469</v>
       </c>
       <c r="M8" t="n">
-        <v>827</v>
+        <v>762</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="P8" t="n">
-        <v>826</v>
+        <v>761</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2084343838894806</v>
+        <v>0.09404607767134407</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1141849013605378</v>
+        <v>0.04945692450468183</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43364</v>
@@ -4493,56 +4119,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>688</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>472</v>
+        <v>74</v>
       </c>
       <c r="AC8" t="n">
-        <v>-388</v>
+        <v>-786</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.7938399361148245</v>
+        <v>0.2063091435813786</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0305387276236266</v>
+        <v>-0.09526670447948257</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.04590682013605585</v>
+        <v>0.3174183799852011</v>
       </c>
       <c r="AH8" t="n">
-        <v>-195</v>
+        <v>-593</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.01623071072076115</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.04057498697634487</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -4554,7 +4172,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4585,35 +4203,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>40361</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40469</v>
+        <v>40569</v>
       </c>
       <c r="M9" t="n">
-        <v>762</v>
+        <v>831</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="P9" t="n">
-        <v>761</v>
+        <v>830</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.09404607767134407</v>
+        <v>0.2136004520679759</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.04945692450468183</v>
+        <v>0.1172972905361221</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43364</v>
@@ -4626,40 +4244,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>688</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>74</v>
+        <v>476</v>
       </c>
       <c r="AC9" t="n">
-        <v>-786</v>
+        <v>-384</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2063091435813786</v>
+        <v>0.7718745829433944</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.09526670447948257</v>
+        <v>-0.02742633844804228</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3174183799852011</v>
+        <v>0.05281751191639561</v>
       </c>
       <c r="AH9" t="n">
-        <v>-593</v>
+        <v>-191</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4670,143 +4288,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40569</v>
-      </c>
-      <c r="M10" t="n">
-        <v>831</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="P10" t="n">
-        <v>830</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2136004520679759</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1172972905361221</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>355</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>476</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-384</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.7718745829433944</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.02742633844804228</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.05281751191639561</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-191</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01934309989634547</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.03366429519600511</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4819,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5302,7 +4783,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5312,7 +4793,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5323,13 +4804,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -5339,25 +4824,25 @@
         <v>43458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43563</v>
+        <v>43578</v>
       </c>
       <c r="M4" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="P4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04842997312606301</v>
+        <v>0.07584506561778712</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.03001802059473596</v>
+        <v>0.0487082053456738</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43880</v>
@@ -5376,34 +4861,34 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1610184600319384</v>
+        <v>0.237203771672156</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0186901847509379</v>
+        <v>-6.245004513516506e-17</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.053038457859234</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5423,7 +4908,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5454,7 +4939,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -5479,10 +4964,10 @@
         <v>140</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.07584506561778712</v>
+        <v>0.07584506561778721</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.0487082053456738</v>
+        <v>0.04870820534567386</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43880</v>
@@ -5522,7 +5007,7 @@
         <v>0.237203771672156</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-6.245004513516506e-17</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
@@ -5548,7 +5033,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5566,24 +5051,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -5592,26 +5073,24 @@
       <c r="K6" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>43578</v>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>145</v>
+        <v>353</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1917257101080129</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751377</v>
       </c>
       <c r="P6" t="n">
-        <v>140</v>
+        <v>349</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.1102712025849563</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.04870820534567386</v>
+        <v>0.1102712025849563</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43880</v>
@@ -5620,9 +5099,11 @@
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.04106856683036175</v>
+      </c>
       <c r="W6" t="n">
         <v>64</v>
       </c>
@@ -5630,50 +5111,38 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1917257101080129</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751377</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>81</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
         <v>0.237203771672156</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>0.06156299723928247</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.0186901847509379</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.053038457859234</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -5685,7 +5154,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5716,7 +5185,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -5725,24 +5194,26 @@
       <c r="K7" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>43760</v>
+      </c>
       <c r="M7" t="n">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1917257101080129</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="P7" t="n">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1102712025849563</v>
+        <v>0.06704482700048213</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.1102712025849563</v>
+        <v>0.05887690428779961</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43880</v>
@@ -5751,11 +5222,9 @@
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.04106856683036175</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
         <v>64</v>
       </c>
@@ -5763,33 +5232,37 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1917257101080129</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>208</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>132</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
         <v>0.237203771672156</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.06156299723928247</v>
+        <v>0.01016869894212575</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>127</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -5806,7 +5279,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5824,24 +5297,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -5850,26 +5319,24 @@
       <c r="K8" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>43760</v>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>272</v>
+        <v>353</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1917257101080134</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751383</v>
       </c>
       <c r="P8" t="n">
-        <v>267</v>
+        <v>349</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.06704482700048213</v>
+        <v>0.1102712025849567</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05887690428779961</v>
+        <v>0.1102712025849567</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43880</v>
@@ -5878,9 +5345,11 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.04106856683036197</v>
+      </c>
       <c r="W8" t="n">
         <v>64</v>
       </c>
@@ -5888,50 +5357,38 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1917257101080134</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751383</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>208</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>132</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.2372037716721567</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.01016869894212575</v>
+        <v>0.0615629972392828</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>127</v>
-      </c>
+        <v>-4.440892098500626e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.02885888369306365</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.053038457859234</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>137</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -5943,7 +5400,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5974,7 +5431,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -5983,24 +5440,26 @@
       <c r="K9" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>43760</v>
+      </c>
       <c r="M9" t="n">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1917257101080134</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="P9" t="n">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1102712025849567</v>
+        <v>0.06704482700048213</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1102712025849567</v>
+        <v>0.05887690428779961</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43880</v>
@@ -6009,11 +5468,9 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.04106856683036197</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
         <v>64</v>
       </c>
@@ -6021,33 +5478,37 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1917257101080134</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>208</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>132</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2372037716721567</v>
+        <v>0.237203771672156</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.0615629972392828</v>
+        <v>0.01016869894212575</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-4.440892098500626e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>127</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -6055,143 +5516,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>43760</v>
-      </c>
-      <c r="M10" t="n">
-        <v>272</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.191725710108013</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1941024876751378</v>
-      </c>
-      <c r="P10" t="n">
-        <v>267</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06704482700048213</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.05887690428779961</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.191725710108013</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1941024876751378</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>208</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>132</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.237203771672156</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.01016869894212575</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>127</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.02885888369306365</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.053038457859234</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>137</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6204,7 +5528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6687,7 +6011,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6697,7 +6021,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6708,13 +6032,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -6724,25 +6052,25 @@
         <v>43913</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>44055</v>
+        <v>44018</v>
       </c>
       <c r="M4" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="P4" t="n">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1125125693043114</v>
+        <v>0.1312987302681534</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05731448931557177</v>
+        <v>0.05908904513265958</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>44564</v>
@@ -6761,34 +6089,34 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3977065718584074</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.001774555817087832</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02049489087797063</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6808,7 +6136,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6839,7 +6167,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -6864,10 +6192,10 @@
         <v>94</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1312987302681534</v>
+        <v>0.1312987302681535</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.05908904513265958</v>
+        <v>0.05908904513265961</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>44564</v>
@@ -6907,7 +6235,7 @@
         <v>0.438925815830939</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
@@ -6933,7 +6261,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6951,24 +6279,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -6993,10 +6317,10 @@
         <v>94</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1312987302681535</v>
+        <v>0.1312987302681534</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05908904513265961</v>
+        <v>0.05908904513265957</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>44564</v>
@@ -7036,7 +6360,7 @@
         <v>0.438925815830939</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-3.469446951953614e-17</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
@@ -7047,18 +6371,10 @@
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.001774555817087832</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.02049489087797063</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-27</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -7070,7 +6386,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7101,7 +6417,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -7126,10 +6442,10 @@
         <v>94</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1312987302681534</v>
+        <v>0.1312987302681535</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05908904513265957</v>
+        <v>0.05908904513265961</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>44564</v>
@@ -7169,7 +6485,7 @@
         <v>0.438925815830939</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-3.469446951953614e-17</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
@@ -7195,7 +6511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7213,24 +6529,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -7246,19 +6558,19 @@
         <v>95</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="P8" t="n">
         <v>94</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1312987302681535</v>
+        <v>0.1312987302681534</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05908904513265961</v>
+        <v>0.05908904513265959</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>44564</v>
@@ -7277,10 +6589,10 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7295,13 +6607,13 @@
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.4389258158309386</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -7309,18 +6621,10 @@
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.001774555817087832</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.02049489087797063</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-27</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -7332,7 +6636,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7363,7 +6667,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -7379,19 +6683,19 @@
         <v>95</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="P9" t="n">
         <v>94</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1312987302681534</v>
+        <v>0.1312987302681535</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05908904513265959</v>
+        <v>0.05908904513265961</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>44564</v>
@@ -7410,10 +6714,10 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -7428,13 +6732,13 @@
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4389258158309386</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-1.387778780781446e-17</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -7448,143 +6752,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M10" t="n">
-        <v>95</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="P10" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1312987302681535</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.05908904513265961</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>72</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.438925815830939</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.001774555817087832</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.02049489087797063</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-27</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7597,7 +6764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8080,7 +7247,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8090,7 +7257,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8101,87 +7268,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45182</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>425</v>
+        <v>513</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="P4" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.135142485096232</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.09955472383307543</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-195</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>-220</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.05506634933016838</v>
+        <v>-0.1546210731632438</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.06979779084367843</v>
+        <v>0.298221368786892</v>
       </c>
       <c r="AH4" t="n">
-        <v>-9</v>
+        <v>-239</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8190,8 +7357,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.3125812952861471</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.2377963300225924</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8201,7 +7372,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8232,77 +7403,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45182</v>
+      </c>
       <c r="M5" t="n">
-        <v>513</v>
+        <v>425</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.0006360007504951526</v>
+        <v>0.135142485096232</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.09955472383307543</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X5" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AC5" t="n">
-        <v>-220</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1546210731632438</v>
+        <v>-0.05506634933016838</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.298221368786892</v>
+        <v>0.06979779084367843</v>
       </c>
       <c r="AH5" t="n">
-        <v>-239</v>
+        <v>-9</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8315,7 +7490,7 @@
         <v>0.3125812952861471</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.2377963300225924</v>
+        <v>-0.08318174614964868</v>
       </c>
     </row>
     <row r="6">
@@ -8326,7 +7501,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8344,52 +7519,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>44846</v>
+        <v>44848</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45182</v>
+        <v>45448</v>
       </c>
       <c r="M6" t="n">
-        <v>425</v>
+        <v>608</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="P6" t="n">
-        <v>424</v>
+        <v>607</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.135142485096232</v>
+        <v>0.2022641315224792</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.09955472383307543</v>
+        <v>0.1781528162115753</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>45707</v>
@@ -8402,62 +7573,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>230</v>
+        <v>411</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>191</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0.3948726900390234</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.05506634933016838</v>
+        <v>0.0235317430483315</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.06979779084367843</v>
+        <v>0.01513267341070224</v>
       </c>
       <c r="AH6" t="n">
-        <v>-9</v>
+        <v>172</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.3125812952861471</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.08318174614964868</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8467,7 +7626,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8498,35 +7657,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>44848</v>
+        <v>44995</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45448</v>
+        <v>45344</v>
       </c>
       <c r="M7" t="n">
-        <v>608</v>
+        <v>536</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="P7" t="n">
-        <v>607</v>
+        <v>535</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2022641315224792</v>
+        <v>0.1869460824536023</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.1781528162115753</v>
+        <v>0.1546210731632438</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>45707</v>
@@ -8539,40 +7698,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>197</v>
+        <v>297</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>411</v>
+        <v>239</v>
       </c>
       <c r="AC7" t="n">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3948726900390234</v>
+        <v>0.4249507686937986</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.0235317430483315</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.01513267341070224</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8592,7 +7751,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8610,114 +7769,98 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45344</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="P8" t="n">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1869460824536023</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1546210731632438</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>102</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>19</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4249507686937986</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>-0.1546210731632438</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.298221368786892</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-239</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.05506634933016838</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.06979779084367843</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -8729,7 +7872,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8760,77 +7903,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45182</v>
+      </c>
       <c r="M9" t="n">
-        <v>513</v>
+        <v>425</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.0006360007504951526</v>
+        <v>0.135142485096232</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.09955472383307543</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AC9" t="n">
-        <v>-220</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1546210731632438</v>
+        <v>-0.05506634933016838</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.298221368786892</v>
+        <v>0.06979779084367843</v>
       </c>
       <c r="AH9" t="n">
-        <v>-239</v>
+        <v>-9</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8841,143 +7988,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45182</v>
-      </c>
-      <c r="M10" t="n">
-        <v>425</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="P10" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.135142485096232</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09955472383307543</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>195</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>230</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2960478980608379</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.05506634933016838</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.06979779084367843</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8990,7 +8000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9473,7 +8483,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9483,7 +8493,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9494,87 +8504,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45910</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.0622368851691482</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05005289002890904</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>51</v>
+        <v>-55</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01203171259102907</v>
+        <v>-0.0620846026199381</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08615512713526996</v>
+        <v>0.2112316646811809</v>
       </c>
       <c r="AH4" t="n">
-        <v>54</v>
+        <v>-52</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9583,8 +8593,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9594,7 +8608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9625,77 +8639,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45910</v>
+      </c>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.0622368851691482</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.05005289002890904</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>51</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.142957119009109</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.0620846026199381</v>
+        <v>-0.01203171259102907</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2112316646811809</v>
+        <v>0.08615512713526996</v>
       </c>
       <c r="AH5" t="n">
-        <v>-52</v>
+        <v>54</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9708,7 +8726,7 @@
         <v>0.04615004380353627</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.03928937419683753</v>
+        <v>0.0214285775248475</v>
       </c>
     </row>
     <row r="6">
@@ -9719,7 +8737,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9737,119 +8755,103 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45910</v>
-      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.0622368851691482</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05005289002890904</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>51</v>
+        <v>-55</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01203171259102907</v>
+        <v>-0.0620846026199381</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08615512713526996</v>
+        <v>0.2112316646811809</v>
       </c>
       <c r="AH6" t="n">
-        <v>54</v>
+        <v>-52</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
         <v>0.04615004380353627</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.0214285775248475</v>
+        <v>-0.03928937419683753</v>
       </c>
     </row>
     <row r="7">
@@ -9860,7 +8862,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9891,77 +8893,81 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45910</v>
+      </c>
       <c r="M7" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.0622368851691482</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0</v>
+        <v>0.05005289002890904</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>51</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.142957119009109</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0620846026199381</v>
+        <v>-0.01203171259102907</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2112316646811809</v>
+        <v>0.08615512713526996</v>
       </c>
       <c r="AH7" t="n">
-        <v>-52</v>
+        <v>54</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9974,7 +8980,7 @@
         <v>0.04615004380353627</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.03928937419683753</v>
+        <v>0.0214285775248475</v>
       </c>
     </row>
     <row r="8">
@@ -9985,7 +8991,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10003,119 +9009,103 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45910</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.0622368851691482</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05005289002890904</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>51</v>
+        <v>-55</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01203171259102907</v>
+        <v>-0.0620846026199381</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.08615512713526996</v>
+        <v>0.2112316646811809</v>
       </c>
       <c r="AH8" t="n">
-        <v>54</v>
+        <v>-52</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
         <v>0.04615004380353627</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.0214285775248475</v>
+        <v>-0.03928937419683753</v>
       </c>
     </row>
     <row r="9">
@@ -10126,7 +9116,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10157,77 +9147,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45910</v>
+      </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.0622368851691482</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.05005289002890904</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>51</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.142957119009109</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.0620846026199381</v>
+        <v>-0.01203171259102907</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2112316646811809</v>
+        <v>0.08615512713526996</v>
       </c>
       <c r="AH9" t="n">
-        <v>-52</v>
+        <v>54</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10240,147 +9234,6 @@
         <v>0.04615004380353627</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.03928937419683753</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M10" t="n">
-        <v>140</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P10" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>106</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>51</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.142957119009109</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.01203171259102907</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.08615512713526996</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>54</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>0.0214285775248475</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.183311285476965</v>
       </c>
       <c r="AD3" s="3" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>3/6</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2/5</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1048,51 +1049,51 @@
         <v>0.4389258158309386</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1197,51 +1198,51 @@
         <v>0.8262952081884098</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1346,51 +1347,51 @@
         <v>1.136324125574051</v>
       </c>
       <c r="AD6" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF6" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH6" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2/5</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1495,51 +1496,51 @@
         <v>1.136324125574051</v>
       </c>
       <c r="AD7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>2/6</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>1/5</t>
-        </is>
-      </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1644,51 +1645,51 @@
         <v>0.8705620217548211</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr"/>
@@ -1793,51 +1794,51 @@
         <v>0.978039755285139</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -2142,66 +2143,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.09032004823014485</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.04076898034342919</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493449</v>
+        <v>0.204425521991354</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2249,66 +2252,68 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+        <v>36076</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>36117</v>
+      </c>
       <c r="M3" t="n">
-        <v>1896</v>
+        <v>87</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="P3" t="n">
-        <v>1889</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.1007681391452584</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.04574573788463201</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-0.08522544924691133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>583</v>
+        <v>58</v>
       </c>
       <c r="X3" t="n">
-        <v>-55</v>
+        <v>27</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-26</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.090950676343116</v>
+        <v>0.2414774038129024</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2316,9 +2321,11 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -2370,34 +2377,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>36880</v>
+        <v>36076</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>39065</v>
+        <v>36117</v>
       </c>
       <c r="M4" t="n">
-        <v>1692</v>
+        <v>87</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2167155682491533</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="P4" t="n">
-        <v>1684</v>
+        <v>85</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1744939914476272</v>
+        <v>0.1007681391452584</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1648448146697581</v>
+        <v>0.04574573788463201</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2407,39 +2414,43 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>189</v>
+        <v>58</v>
       </c>
       <c r="X4" t="n">
-        <v>-449</v>
+        <v>27</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2167155682491533</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1503</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-26</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.276675444403685</v>
+        <v>0.2414774038129024</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1535435964052177</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3050330739766358</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -2491,34 +2502,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>37460</v>
+        <v>36076</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>39192</v>
+        <v>36117</v>
       </c>
       <c r="M5" t="n">
-        <v>1777</v>
+        <v>87</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.431970132651427</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="P5" t="n">
-        <v>1769</v>
+        <v>85</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2308297845907774</v>
+        <v>0.1007681391452584</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.2234724854190869</v>
+        <v>0.04574573788463201</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2528,39 +2539,43 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>583</v>
+        <v>58</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>27</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.431970132651427</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1194</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-26</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.7604708088110927</v>
+        <v>0.2414774038129024</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.0949159256558888</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.08977850957436206</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -2612,66 +2627,68 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+        <v>36076</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>36117</v>
+      </c>
       <c r="M6" t="n">
-        <v>1896</v>
+        <v>87</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="P6" t="n">
-        <v>1889</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.1007681391452584</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.04574573788463201</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-0.08522544924691133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>58</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>27</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-26</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>1.090950676343116</v>
+        <v>0.2414774038129024</v>
       </c>
       <c r="AF6" s="3" t="n">
         <v>0</v>
@@ -2679,9 +2696,11 @@
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -2733,66 +2752,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36076</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36117</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>87</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="P7" t="n">
-        <v>1889</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.1007681391452584</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.04574573788463201</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.08522544924691133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>583</v>
+        <v>58</v>
       </c>
       <c r="X7" t="n">
-        <v>-55</v>
+        <v>27</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-26</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.090950676343116</v>
+        <v>0.2414774038129024</v>
       </c>
       <c r="AF7" s="3" t="n">
         <v>0</v>
@@ -2800,9 +2821,11 @@
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -2854,83 +2877,87 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>37460</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>1896</v>
+        <v>90</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4547344877239885</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4654013134181593</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1889</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2744558031825254</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2744558031825254</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.06129877473879142</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
+        <v>-31</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
         <v>-55</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>-0.4547344877239885</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>-0.4654013134181593</v>
-      </c>
-      <c r="AA8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.8339689151178216</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.04393260789245035</v>
+        <v>-0.04574573788463201</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.06701415450180059</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>0.1945080942039396</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-29</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.3106955008082057</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.2164333699121769</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2975,34 +3002,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>39356</v>
+        <v>36105</v>
       </c>
       <c r="M9" t="n">
-        <v>1890</v>
+        <v>79</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4755463220216952</v>
+        <v>-0.1638829728650905</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4858060135695987</v>
+        <v>-0.1638829728650905</v>
       </c>
       <c r="P9" t="n">
-        <v>1882</v>
+        <v>78</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2633859495049935</v>
+        <v>0.09202955837544459</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2629690893922373</v>
+        <v>0.0398344104474557</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -3012,46 +3039,54 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X9" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4755463220216952</v>
+        <v>-0.1638829728650905</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4858060135695987</v>
+        <v>-0.1638829728650905</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1307</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.9067460902454902</v>
+        <v>0.196004826533269</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.05541932168273839</v>
+        <v>-0.00591132743717631</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.04620232020409387</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.03062512133884909</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.3106955008082057</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.05120697764807369</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3348,68 +3383,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573142</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922748</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388257</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459449</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573142</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616548</v>
+        <v>0.9463998245842093</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3457,68 +3490,66 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.5248897185497376</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.5311044950287365</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>40843</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1022</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.4884434813691406</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.4884434813691406</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1021</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2376717026529739</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1447236289841644</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>-0.09123353816587243</v>
+      </c>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5248897185497376</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>667</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-193</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.9548182137849031</v>
+        <v>1.104774489298621</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3526,11 +3557,9 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -3582,34 +3611,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>36880</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>39065</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1691</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2218600516750671</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.232038669223518</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1688</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1745455482492981</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1648882806730631</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39412</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>41402</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1404</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1193545340586639</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1193545340586639</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1403</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.08442792929102155</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.06024880670250294</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3619,43 +3648,39 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="X4" t="n">
-        <v>-322</v>
+        <v>-449</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.2218600516750671</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.232038669223518</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1371</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>511</v>
-      </c>
+        <v>1503</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1355307427048227</v>
+        <v>0.2851158742751292</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.08447482228166148</v>
+        <v>-0.1535840825223102</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3690889473104767</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>704</v>
-      </c>
+        <v>0.3030296668746706</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -3707,34 +3732,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>39204</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1784</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.4357008594724194</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.4430822889269979</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.230380158877041</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.2235347347718778</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>40900</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1062</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1061</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1949570049202901</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1210123309070127</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -3744,43 +3769,39 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4357008594724194</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4430822889269979</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>707</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-153</v>
-      </c>
+        <v>1202</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.7718745829433944</v>
+        <v>0.7721097343247225</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.02371129807715167</v>
+        <v>-0.09493762842349548</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.05281751191639561</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>40</v>
-      </c>
+        <v>0.08918885907731822</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -3832,80 +3853,76 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.5248897185497376</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.5311044950287365</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40094</v>
-      </c>
-      <c r="M6" t="n">
-        <v>504</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2869026592132757</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2869026592132757</v>
-      </c>
-      <c r="P6" t="n">
-        <v>503</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1066435614404946</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.0456251682558669</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.09123353816587243</v>
+      </c>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.5248897185497376</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>149</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-711</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4023330936793994</v>
+        <v>1.104774489298621</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0990984607282975</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.2015408221558649</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-518</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -3957,80 +3974,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.5248897185497376</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.5311044950287365</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40563</v>
-      </c>
-      <c r="M7" t="n">
-        <v>827</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.4425366612330848</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.4425366612330848</v>
-      </c>
-      <c r="P7" t="n">
-        <v>826</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.2084343838894806</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1141849013605378</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.09123353816587243</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.5248897185497376</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>472</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-388</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.7938399361148245</v>
+        <v>1.104774489298621</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0305387276236266</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.04590682013605585</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-195</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4082,80 +4095,76 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.4583157020018671</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.4654013134181593</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2745281712268109</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2745281712268109</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>40361</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>40469</v>
-      </c>
-      <c r="M8" t="n">
-        <v>762</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1710251013839396</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1710251013839396</v>
-      </c>
-      <c r="P8" t="n">
-        <v>761</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.09404607767134407</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04945692450468183</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.06746401012390801</v>
+      </c>
       <c r="W8" t="n">
-        <v>688</v>
+        <v>582</v>
       </c>
       <c r="X8" t="n">
-        <v>333</v>
+        <v>-55</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.4583157020018671</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>74</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-786</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2063091435813786</v>
+        <v>0.8460937555244528</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.09526670447948257</v>
+        <v>-0.04394419196856231</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.3174183799852011</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-593</v>
-      </c>
+        <v>0.06657401654787054</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -4207,34 +4216,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>39360</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1893</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.4789908475920401</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4858060135695986</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1890</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.263178511221564</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.2630396673653051</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40569</v>
-      </c>
-      <c r="M9" t="n">
-        <v>831</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="P9" t="n">
-        <v>830</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.2136004520679759</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.1172972905361221</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4244,43 +4253,39 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4789908475920401</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4858060135695986</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>476</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-384</v>
-      </c>
+        <v>1311</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.7718745829433944</v>
+        <v>0.9193520792835927</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.02742633844804228</v>
+        <v>-0.05543269583006816</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.05281751191639561</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-191</v>
-      </c>
+        <v>0.04589887095769751</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -4584,34 +4589,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.0826944425385638</v>
+        <v>0.2354171526922748</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687856</v>
+        <v>0.1563175570682506</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -4621,22 +4626,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -4645,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160745</v>
+        <v>1.014136226616548</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -4693,34 +4698,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43578</v>
+        <v>40843</v>
       </c>
       <c r="M3" t="n">
-        <v>145</v>
+        <v>1022</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="P3" t="n">
-        <v>140</v>
+        <v>1021</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.2376717026529739</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.04870820534567386</v>
+        <v>0.1447498636674188</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -4730,31 +4735,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>81</v>
+        <v>667</v>
       </c>
       <c r="AC3" t="n">
-        <v>5</v>
+        <v>-193</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.9548182137849031</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -4818,34 +4823,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39412</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43578</v>
+        <v>41402</v>
       </c>
       <c r="M4" t="n">
-        <v>145</v>
+        <v>1404</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="P4" t="n">
-        <v>140</v>
+        <v>1403</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.07584506561778712</v>
+        <v>0.08442792929102155</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0487082053456738</v>
+        <v>0.06025972826639261</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -4855,40 +4860,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>81</v>
+        <v>1371</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>511</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.1355307427048227</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-6.245004513516506e-17</v>
+        <v>-0.08449013540102621</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0</v>
+        <v>0.3690889473104767</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>704</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4943,34 +4948,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43578</v>
+        <v>40900</v>
       </c>
       <c r="M5" t="n">
-        <v>145</v>
+        <v>1062</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="P5" t="n">
-        <v>140</v>
+        <v>1061</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.1949570049202901</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.04870820534567386</v>
+        <v>0.121034267339878</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4980,40 +4985,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>81</v>
+        <v>707</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>-153</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.7718745829433944</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0</v>
+        <v>-0.02371559632754085</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>0.05281751191639561</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5068,76 +5073,80 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+        <v>39881</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>40094</v>
+      </c>
       <c r="M6" t="n">
-        <v>353</v>
+        <v>504</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1917257101080129</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="P6" t="n">
-        <v>349</v>
+        <v>503</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1102712025849563</v>
+        <v>0.1066435614404946</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1102712025849563</v>
+        <v>0.04563343892905291</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-0.04106856683036175</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1917257101080129</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-711</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.4023330936793994</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.06156299723928247</v>
+        <v>-0.0991164247383659</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>0.2015408221558649</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-518</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -5189,34 +5198,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43760</v>
+        <v>40563</v>
       </c>
       <c r="M7" t="n">
-        <v>272</v>
+        <v>827</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="P7" t="n">
-        <v>267</v>
+        <v>826</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.06704482700048213</v>
+        <v>0.2084343838894806</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05887690428779961</v>
+        <v>0.11420560015548</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5226,40 +5235,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>208</v>
+        <v>472</v>
       </c>
       <c r="AC7" t="n">
-        <v>132</v>
+        <v>-388</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.7938399361148245</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.01016869894212575</v>
+        <v>-0.03054426351193883</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
+        <v>0.04590682013605585</v>
       </c>
       <c r="AH7" t="n">
-        <v>127</v>
+        <v>-195</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5314,76 +5323,80 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+        <v>40361</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>40469</v>
+      </c>
       <c r="M8" t="n">
-        <v>353</v>
+        <v>762</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1917257101080134</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="P8" t="n">
-        <v>349</v>
+        <v>761</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1102712025849567</v>
+        <v>0.09404607767134407</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1102712025849567</v>
+        <v>0.04946588977703041</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.04106856683036197</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>688</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1917257101080134</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-786</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2372037716721567</v>
+        <v>0.2063091435813786</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.0615629972392828</v>
+        <v>-0.09528397389038841</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-4.440892098500626e-16</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>0.3174183799852011</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-593</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -5435,34 +5448,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43760</v>
+        <v>40569</v>
       </c>
       <c r="M9" t="n">
-        <v>272</v>
+        <v>831</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="P9" t="n">
-        <v>267</v>
+        <v>830</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.06704482700048213</v>
+        <v>0.2136004520679759</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05887690428779961</v>
+        <v>0.1173185535274209</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -5472,40 +5485,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>208</v>
+        <v>476</v>
       </c>
       <c r="AC9" t="n">
-        <v>132</v>
+        <v>-384</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.7718745829433944</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.01016869894212575</v>
+        <v>-0.02743131013999792</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
+        <v>0.05281751191639561</v>
       </c>
       <c r="AH9" t="n">
-        <v>127</v>
+        <v>-191</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -5812,34 +5825,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606707</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.202297991486007</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428304</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.0521184671904906</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425156</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440424</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5849,22 +5862,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5873,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5921,34 +5934,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M3" t="n">
+        <v>146</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1935462542088221</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1941024876751378</v>
+      </c>
+      <c r="P3" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.07558961362210245</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.04864146159510002</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M3" t="n">
-        <v>95</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="P3" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1312987302681535</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.05908904513265961</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5958,31 +5971,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.2399967204801585</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6046,34 +6059,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M4" t="n">
+        <v>146</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1935462542088222</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1941024876751379</v>
+      </c>
+      <c r="P4" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.07558961362210237</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.04864146159509995</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M4" t="n">
-        <v>95</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="P4" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1312987302681534</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05908904513265958</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6083,37 +6096,37 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088222</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751379</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="AC4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.2399967204801587</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-2.775557561562891e-17</v>
+        <v>-6.938893903907228e-17</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -6171,34 +6184,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M5" t="n">
+        <v>146</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1935462542088221</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1941024876751378</v>
+      </c>
+      <c r="P5" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.07558961362210245</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.04864146159510002</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M5" t="n">
-        <v>95</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="P5" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1312987302681535</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.05908904513265961</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6208,31 +6221,31 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="AC5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.2399967204801585</v>
       </c>
       <c r="AF5" s="3" t="n">
         <v>0</v>
@@ -6296,80 +6309,76 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>354</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.193546254208822</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1941024876751377</v>
+      </c>
+      <c r="P6" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1101166241880352</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1101166241880352</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M6" t="n">
-        <v>95</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="P6" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1312987302681534</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.05908904513265957</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.04322844867439612</v>
+      </c>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.193546254208822</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751377</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>72</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>17</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.2399967204801583</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-3.469446951953614e-17</v>
+        <v>0.06147516259293521</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -6421,34 +6430,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43761</v>
+      </c>
+      <c r="M7" t="n">
+        <v>274</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1935462542088221</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1941024876751378</v>
+      </c>
+      <c r="P7" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.06680237592703646</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05879549884831063</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M7" t="n">
-        <v>95</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="P7" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1312987302681535</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.05908904513265961</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -6458,40 +6467,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="AC7" t="n">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.2399967204801585</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0</v>
+        <v>0.01015403725321061</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -6546,80 +6555,76 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>354</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1935462542088225</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1941024876751383</v>
+      </c>
+      <c r="P8" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1101166241880356</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1101166241880356</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M8" t="n">
-        <v>95</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3050371402068921</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3050371402068921</v>
-      </c>
-      <c r="P8" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1312987302681534</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.05908904513265959</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.04322844867439635</v>
+      </c>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.1935462542088225</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.1941024876751383</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>72</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>17</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4389258158309386</v>
+        <v>0.2399967204801592</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-1.387778780781446e-17</v>
+        <v>0.06147516259293553</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
+        <v>-4.440892098500626e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -6671,34 +6676,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43761</v>
+      </c>
+      <c r="M9" t="n">
+        <v>274</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1935462542088221</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1941024876751378</v>
+      </c>
+      <c r="P9" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.06680237592703646</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05879549884831063</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="M9" t="n">
-        <v>95</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="P9" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1312987302681535</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.05908904513265961</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6708,40 +6713,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="AC9" t="n">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.2399967204801585</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0</v>
+        <v>0.01015403725321061</v>
       </c>
       <c r="AG9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7048,34 +7053,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425156</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440424</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996989</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694574</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7085,22 +7090,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7109,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088539</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7157,34 +7162,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="M3" t="n">
+        <v>95</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="P3" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1312987302681535</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05908904513265961</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45344</v>
-      </c>
-      <c r="M3" t="n">
-        <v>536</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.298221368786892</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.298221368786892</v>
-      </c>
-      <c r="P3" t="n">
-        <v>535</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1869460824536023</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1546210731632438</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -7194,31 +7199,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4249507686937986</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -7282,73 +7287,77 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="M4" t="n">
+        <v>95</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="P4" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1312987302681534</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05908904513265958</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>513</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.00942253736259735</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.0006360007504951526</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AC4" t="n">
-        <v>-220</v>
+        <v>17</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1546210731632438</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.298221368786892</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-239</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -7357,12 +7366,8 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.3125812952861471</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.2377963300225924</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7407,34 +7412,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="M5" t="n">
+        <v>95</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="P5" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1312987302681535</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.05908904513265961</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45182</v>
-      </c>
-      <c r="M5" t="n">
-        <v>425</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="P5" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.135142485096232</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.09955472383307543</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -7444,40 +7449,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.05506634933016838</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.06979779084367843</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -7486,12 +7491,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.3125812952861471</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.08318174614964868</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7536,34 +7537,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="M6" t="n">
+        <v>95</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="P6" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1312987302681534</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.05908904513265957</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45448</v>
-      </c>
-      <c r="M6" t="n">
-        <v>608</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2830886953761897</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2830886953761897</v>
-      </c>
-      <c r="P6" t="n">
-        <v>607</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.2022641315224792</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1781528162115753</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7573,40 +7574,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>411</v>
+        <v>72</v>
       </c>
       <c r="AC6" t="n">
-        <v>191</v>
+        <v>17</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3948726900390234</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.0235317430483315</v>
+        <v>-3.469446951953614e-17</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.01513267341070224</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -7661,34 +7662,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="M7" t="n">
+        <v>95</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="P7" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1312987302681535</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05908904513265961</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45344</v>
-      </c>
-      <c r="M7" t="n">
-        <v>536</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.298221368786892</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.298221368786892</v>
-      </c>
-      <c r="P7" t="n">
-        <v>535</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1869460824536023</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1546210731632438</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7698,31 +7699,31 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4249507686937986</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF7" s="3" t="n">
         <v>0</v>
@@ -7786,73 +7787,77 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="M8" t="n">
+        <v>95</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3050371402068921</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3050371402068921</v>
+      </c>
+      <c r="P8" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1312987302681534</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.05908904513265959</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>513</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.00942253736259735</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.0006360007504951526</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AC8" t="n">
-        <v>-220</v>
+        <v>17</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0</v>
+        <v>0.4389258158309386</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.1546210731632438</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.298221368786892</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AH8" t="n">
-        <v>-239</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -7907,34 +7912,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="M9" t="n">
+        <v>95</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="P9" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1312987302681535</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05908904513265961</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45182</v>
-      </c>
-      <c r="M9" t="n">
-        <v>425</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="P9" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.135142485096232</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09955472383307543</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -7944,40 +7949,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0.438925815830939</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.05506634933016838</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06979779084367843</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8284,34 +8289,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996989</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694574</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451827</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -8321,22 +8326,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -8345,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088539</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8393,34 +8398,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="M3" t="n">
+        <v>536</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="P3" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1869460824536023</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1546210731632438</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45832</v>
-      </c>
-      <c r="M3" t="n">
-        <v>86</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2112316646811809</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2112316646811809</v>
-      </c>
-      <c r="P3" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.0982771437968664</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.0620846026199381</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8430,31 +8435,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>297</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2112316646811809</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2112316646811809</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>52</v>
+        <v>239</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3</v>
+        <v>19</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2677993717836067</v>
+        <v>0.4249507686937986</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8518,30 +8523,30 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -8554,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -8569,7 +8574,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
@@ -8578,13 +8583,13 @@
         <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0620846026199381</v>
+        <v>-0.1546210731632438</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.2112316646811809</v>
+        <v>0.298221368786892</v>
       </c>
       <c r="AH4" t="n">
-        <v>-52</v>
+        <v>-239</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8594,10 +8599,10 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" s="3" t="n">
-        <v>0.04615004380353627</v>
+        <v>0.3125812952861471</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.03928937419683753</v>
+        <v>-0.2377963300225924</v>
       </c>
     </row>
     <row r="5">
@@ -8643,34 +8648,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45182</v>
+      </c>
+      <c r="M5" t="n">
+        <v>425</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="P5" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.135142485096232</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.09955472383307543</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M5" t="n">
-        <v>140</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P5" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -8680,40 +8685,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AC5" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.01203171259102907</v>
+        <v>-0.05506634933016838</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.08615512713526996</v>
+        <v>0.06979779084367843</v>
       </c>
       <c r="AH5" t="n">
-        <v>54</v>
+        <v>-9</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8723,10 +8728,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.04615004380353627</v>
+        <v>0.3125812952861471</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>0.0214285775248475</v>
+        <v>-0.08318174614964868</v>
       </c>
     </row>
     <row r="6">
@@ -8772,73 +8777,77 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45448</v>
+      </c>
+      <c r="M6" t="n">
+        <v>608</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2830886953761897</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.2830886953761897</v>
+      </c>
+      <c r="P6" t="n">
+        <v>607</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.2022641315224792</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1781528162115753</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>88</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="X6" t="n">
-        <v>-34</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="AC6" t="n">
-        <v>-55</v>
+        <v>191</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0</v>
+        <v>0.3948726900390234</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0620846026199381</v>
+        <v>0.0235317430483315</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.2112316646811809</v>
+        <v>0.01513267341070224</v>
       </c>
       <c r="AH6" t="n">
-        <v>-52</v>
+        <v>172</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -8847,12 +8856,8 @@
       <c r="AK6" s="3" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" s="3" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.03928937419683753</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8897,34 +8902,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="M7" t="n">
+        <v>536</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="P7" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1869460824536023</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1546210731632438</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M7" t="n">
-        <v>140</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P7" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8934,40 +8939,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>34</v>
+        <v>297</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>106</v>
+        <v>239</v>
       </c>
       <c r="AC7" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0.4249507686937986</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.01203171259102907</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.08615512713526996</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8976,12 +8981,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>0.0214285775248475</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9026,30 +9027,30 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -9062,7 +9063,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>0</v>
@@ -9077,7 +9078,7 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
@@ -9086,13 +9087,13 @@
         <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0620846026199381</v>
+        <v>-0.1546210731632438</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.2112316646811809</v>
+        <v>0.298221368786892</v>
       </c>
       <c r="AH8" t="n">
-        <v>-52</v>
+        <v>-239</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -9101,12 +9102,8 @@
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.03928937419683753</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9151,34 +9148,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45182</v>
+      </c>
+      <c r="M9" t="n">
+        <v>425</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="P9" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.135142485096232</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09955472383307543</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M9" t="n">
-        <v>140</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P9" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -9188,40 +9185,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AC9" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.01203171259102907</v>
+        <v>-0.05506634933016838</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.08615512713526996</v>
+        <v>0.06979779084367843</v>
       </c>
       <c r="AH9" t="n">
-        <v>54</v>
+        <v>-9</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -9230,12 +9227,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>0.0214285775248475</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9248,7 +9241,1255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451827</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45832</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2112316646811809</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2112316646811809</v>
+      </c>
+      <c r="P3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.0982771437968664</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.0620846026199381</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.2112316646811809</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.2112316646811809</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>52</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2677993717836067</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>89</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.0620846026199381</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.2112316646811809</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="M5" t="n">
+        <v>140</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="P5" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.0622368851691482</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.05005289002890904</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>34</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>106</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0.142957119009109</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.01203171259102907</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.08615512713526996</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>0.0214285775248475</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>89</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.0620846026199381</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.2112316646811809</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="M7" t="n">
+        <v>140</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="P7" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.0622368851691482</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05005289002890904</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>34</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>106</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.142957119009109</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.01203171259102907</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.08615512713526996</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>0.0214285775248475</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>89</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.0620846026199381</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.2112316646811809</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="M9" t="n">
+        <v>140</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="P9" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.0622368851691482</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05005289002890904</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>106</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.142957119009109</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.01203171259102907</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.08615512713526996</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>0.0214285775248475</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9354,12 +10595,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -9368,10 +10605,10 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -9402,10 +10639,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -9415,7 +10652,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -9448,8 +10685,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -9458,10 +10699,10 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -9534,24 +10775,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9582,21 +10819,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9613,30 +10852,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -9666,15 +10907,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -9683,10 +10920,10 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9713,7 +10950,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -9722,16 +10959,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9758,11 +10993,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -9771,10 +11010,10 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9801,7 +11040,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -9813,13 +11052,13 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9846,22 +11085,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -9881,37 +11118,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="3" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9928,37 +11163,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9985,25 +11218,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.5241379310344828</v>
-      </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -10030,11 +11265,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -10043,10 +11282,10 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -10073,14 +11312,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -10090,7 +11329,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -10120,30 +11359,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
